--- a/UMG_Personaliza_Matriz_y_Asignaciones.xlsx
+++ b/UMG_Personaliza_Matriz_y_Asignaciones.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josef\Documents\Universidad\Desarrollo web\Proyecto_desarrollo_web\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F87FA2A8B94B185E471549236006CED721B5C931" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="📊 Resumen y Progreso" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="✅ Matriz de Requerimientos" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="👥 Asignaciones de Equipo" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="🔐 Roles y Credenciales" state="visible" r:id="rId7"/>
+    <sheet name="📊 Resumen y Progreso" sheetId="1" r:id="rId1"/>
+    <sheet name="✅ Matriz de Requerimientos" sheetId="2" r:id="rId2"/>
+    <sheet name="⏳ Pendientes" sheetId="3" r:id="rId3"/>
+    <sheet name="🧪 Evidencia 1ra Revisión" sheetId="4" r:id="rId4"/>
+    <sheet name="👥 Asignaciones de Equipo" sheetId="5" r:id="rId5"/>
+    <sheet name="🔐 Roles y Credenciales" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="570">
   <si>
     <t>UMG PERSONALIZA — MATRIZ DE REQUERIMIENTOS Y ASIGNACIONES</t>
   </si>
@@ -25,22 +36,22 @@
     <t>TOTAL REQUERIMIENTOS</t>
   </si>
   <si>
-    <t>CUMPLIDOS (CÓDIGO/SISTEMA)</t>
-  </si>
-  <si>
-    <t>PENDIENTES EQUIPO (DOCS/VIDEO)</t>
+    <t>CUMPLIDOS (VERIFICADO EN VIVO)</t>
+  </si>
+  <si>
+    <t>PENDIENTES REALES</t>
   </si>
   <si>
     <t>EXTRAS IMPLEMENTADOS</t>
   </si>
   <si>
-    <t>34 (81%)</t>
-  </si>
-  <si>
-    <t>8 (19%)</t>
-  </si>
-  <si>
-    <t>7 (Bonus)</t>
+    <t>38 (88%)</t>
+  </si>
+  <si>
+    <t>5 (12%)</t>
+  </si>
+  <si>
+    <t>8 (Bonus)</t>
   </si>
   <si>
     <t>DESGLOSE POR MÓDULOS DEL PROYECTO</t>
@@ -82,10 +93,10 @@
     <t>4. Carrito, Áreas de Entrega y Checkout</t>
   </si>
   <si>
-    <t>83%</t>
-  </si>
-  <si>
-    <t>🟡 Falta Recurrente Real</t>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>🟡 Bug áreas + reCAPTCHA off</t>
   </si>
   <si>
     <t>5. Tracking en Tiempo Real y Constancia PDF</t>
@@ -100,13 +111,19 @@
     <t>8. Requisitos No Funcionales (Seguridad, OWASP, Docker, BD)</t>
   </si>
   <si>
-    <t>9. Entregables Académicos (Video Inglés, UML, Bizagi, Manuales)</t>
-  </si>
-  <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>🟡 Asignar al Equipo</t>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>🟡 Bitácora sin fallidos</t>
+  </si>
+  <si>
+    <t>9. Entregables Académicos (Video, PPT, UML, Bizagi, Manual, Postman, Deploy)</t>
+  </si>
+  <si>
+    <t>43%</t>
+  </si>
+  <si>
+    <t>🟡 Falta PPT, video, manual y deploy</t>
   </si>
   <si>
     <t>CALENDARIO OFICIAL DE EVALUACIONES (DOC ACADÉMICO)</t>
@@ -133,7 +150,7 @@
     <t>2 pts</t>
   </si>
   <si>
-    <t>✅ 100% Listo en Código</t>
+    <t>✅ Verificada en ejecución</t>
   </si>
   <si>
     <t>2da Revisión</t>
@@ -142,13 +159,16 @@
     <t>Elaboración producto, entrega repartidor, dashboard ventas, proceso de compra, sitio público.</t>
   </si>
   <si>
+    <t>✅ Completa en código</t>
+  </si>
+  <si>
     <t>3ra Revisión</t>
   </si>
   <si>
     <t>Simulacro y pruebas de estrés/integración en vivo.</t>
   </si>
   <si>
-    <t>✅ Pruebas QA 35/35</t>
+    <t>✅ QA 75/75 + esta auditoría</t>
   </si>
   <si>
     <t>Evaluación Final</t>
@@ -160,7 +180,10 @@
     <t>Punteo Final</t>
   </si>
   <si>
-    <t>🟡 En preparación por equipo</t>
+    <t>🟡 Falta PPT, video y manual</t>
+  </si>
+  <si>
+    <t>Auditoría del 20/09/2026 — sistema levantado con Docker y probado en ejecución: 3 contenedores sanos, los 4 logins, el ciclo registro → OTP → login, control de acceso por rol, rate limit y las 59 peticiones del collection Postman. Ver la pestaña «Evidencia 1ra Revisión» y la columna «Observación de auditoría».</t>
   </si>
   <si>
     <t>MATRIZ DE TRAZABILIDAD: REQUERIMIENTOS DOC OFICIAL VS CÓDIGO IMPLEMENTADO</t>
@@ -187,6 +210,12 @@
     <t>Responsable Sugerido</t>
   </si>
   <si>
+    <t>Observación de auditoría — 20/09/2026</t>
+  </si>
+  <si>
+    <t>Cómo se verificó</t>
+  </si>
+  <si>
     <t>REQ-01</t>
   </si>
   <si>
@@ -202,7 +231,7 @@
     <t>✅ Cumplido</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: index.html (Wizard Registro)
+    <t>Frontend: index.html (Wizard Registro)
 Backend: /api/auth/registro
 BD: tabla usuarios</t>
   </si>
@@ -210,6 +239,12 @@
     <t>Sistema Base</t>
   </si>
   <si>
+    <t>POST /registro -&gt; HTTP 201. Usuario id 783 creado y confirmado en la tabla usuarios con todos sus campos.</t>
+  </si>
+  <si>
+    <t>✅ Ejecutado</t>
+  </si>
+  <si>
     <t>REQ-02</t>
   </si>
   <si>
@@ -219,10 +254,16 @@
     <t>Comprador elige: Correo electrónico, WhatsApp o Ambos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: Checkboxes en registro
+    <t>🟡 Cumplido con obs.</t>
+  </si>
+  <si>
+    <t>Frontend: Checkboxes en registro
 BD: Notificaciones_Correo_Usuario, Notificaciones_Whatsapp_Usuario</t>
   </si>
   <si>
+    <t>DEFECTO MENOR: por API el canal se guarda mal. notif_whatsapp="0" queda como 1 porque en JS la cadena "0" es verdadera (registro.js:74-75). Por la interfaz web SI funciona (la casilla sin marcar no se envia). Afecta al collection Postman.</t>
+  </si>
+  <si>
     <t>REQ-03</t>
   </si>
   <si>
@@ -235,6 +276,9 @@
     <t>Backend: bcrypt.hash en backend/routes/auth/registro.js</t>
   </si>
   <si>
+    <t>Comprobado en la base: hash $2b$10$... de 60 caracteres. Es bcrypt con 10 salt rounds, tal como pide el documento.</t>
+  </si>
+  <si>
     <t>REQ-04</t>
   </si>
   <si>
@@ -247,6 +291,12 @@
     <t>Frontend: js/camera.js, js/face-models.js (@vladmandic/face-api)</t>
   </si>
   <si>
+    <t>El backend carga los modelos al arrancar (log: "Modelos faciales cargados correctamente") y calcula descriptores de 128D. El match con cara real no se puede automatizar: requiere camara y persona.</t>
+  </si>
+  <si>
+    <t>🟡 Parcial</t>
+  </si>
+  <si>
     <t>REQ-05</t>
   </si>
   <si>
@@ -259,6 +309,12 @@
     <t>Frontend: js/face-filter-track.js, canvas de captura con stickers</t>
   </si>
   <si>
+    <t>Los 3 filtros existen como assets (hat.png, glasses.png, dog.png) y se posicionan sobre landmarks. Prueba visual pendiente del equipo.</t>
+  </si>
+  <si>
+    <t>🔵 Código</t>
+  </si>
+  <si>
     <t>REQ-06</t>
   </si>
   <si>
@@ -271,6 +327,9 @@
     <t>BD: Avatar_String64_Usuario (modificada) y descriptor biométrico en tabla</t>
   </si>
   <si>
+    <t>Las columnas Foto_String64_Usuario (original) y Avatar_String64_Usuario (modificada) existen y se escriben en el registro.</t>
+  </si>
+  <si>
     <t>REQ-07</t>
   </si>
   <si>
@@ -283,6 +342,9 @@
     <t>Backend: backend/utils/credencial.js (pdf-lib + qrcode) + envío vía Nodemailer/Baileys</t>
   </si>
   <si>
+    <t>credencial.js genera el PDF con QR y codigo de barras. El ENVIO no se pudo verificar: requiere SMTP real configurado.</t>
+  </si>
+  <si>
     <t>REQ-08</t>
   </si>
   <si>
@@ -295,6 +357,9 @@
     <t>Backend: routes/auth/registro.js asigna Rol 6 por defecto</t>
   </si>
   <si>
+    <t>Confirmado en base: el usuario de prueba nacio con Id_Rol_Usuario = 6 sin intervencion.</t>
+  </si>
+  <si>
     <t>REQ-09</t>
   </si>
   <si>
@@ -307,10 +372,13 @@
     <t>1) Usuario/Pass, 2) Cámara con matching biométrico facial, 3) Escaneo de QR de credencial.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: index.html (Pestañas Pass/Facial/QR)
+    <t>Frontend: index.html (Pestañas Pass/Facial/QR)
 Backend: /api/auth/login, /api/auth/login-face, /api/auth/login-qr</t>
   </si>
   <si>
+    <t>Login por contrasena PROBADO con los 4 roles: admin, supervisor, repartidor y test devuelven HTTP 200 con token. Facial y QR existen en codigo pero necesitan camara/credencial fisica.</t>
+  </si>
+  <si>
     <t>REQ-10</t>
   </si>
   <si>
@@ -320,10 +388,13 @@
     <t>Envío de código OTP o enlace de reset al correo/WhatsApp registrado del comprador.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: /recuperar.html
+    <t>Frontend: /recuperar.html
 Backend: /api/auth/forgot-password, /api/auth/reset-password</t>
   </si>
   <si>
+    <t>Ciclo OTP probado entero: codigo incorrecto -&gt; HTTP 400; codigo correcto -&gt; HTTP 200 "Usuario verificado correctamente".</t>
+  </si>
+  <si>
     <t>REQ-11</t>
   </si>
   <si>
@@ -336,6 +407,9 @@
     <t>Backend: JWT con emisión inmediata y validación sub-segundo</t>
   </si>
   <si>
+    <t>JWT emitido con iss, aud y exp de 15 min. El login por contrasena responde en milisegundos, muy por debajo de los 15 s.</t>
+  </si>
+  <si>
     <t>REQ-12</t>
   </si>
   <si>
@@ -348,10 +422,13 @@
     <t>Artículos UMG: playeras, tazas, llaveros, tarjetas de presentación con precio y stock.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: /comprador/tienda.html
+    <t>Frontend: /comprador/tienda.html
 BD: tabla articulos (12 productos base + stock)</t>
   </si>
   <si>
+    <t>CORRECCION: la matriz decia "12 productos base". GET /api/tienda/productos devuelve 6, y los 6 tienen imagen_url = NULL (sin fotografia).</t>
+  </si>
+  <si>
     <t>REQ-13</t>
   </si>
   <si>
@@ -364,6 +441,9 @@
     <t>Frontend: modal de personalización en tienda.js con tabs Lado A / Lado B y canvas interactivo</t>
   </si>
   <si>
+    <t>5 de los 6 productos traen tiene_lado_b = true. El modal de personalizacion maneja lado_a y lado_b por separado.</t>
+  </si>
+  <si>
     <t>REQ-14</t>
   </si>
   <si>
@@ -379,6 +459,9 @@
     <t>Persona E</t>
   </si>
   <si>
+    <t>Buscador en vivo, orden por precio y nombre, y los 3 badges de stock (Agotado / Ultimas N / En stock) presentes en el catalogo servido.</t>
+  </si>
+  <si>
     <t>REQ-15</t>
   </si>
   <si>
@@ -391,10 +474,13 @@
     <t>Vista de carrito con cálculo de subtotales, totales y persistencia de items con diseño Lado A/B.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: /comprador/carrito.html
+    <t>Frontend: /comprador/carrito.html
 Backend: /api/tienda/carrito</t>
   </si>
   <si>
+    <t>Los endpoints de carrito responden correctamente con sesion de comprador.</t>
+  </si>
+  <si>
     <t>REQ-16</t>
   </si>
   <si>
@@ -404,11 +490,17 @@
     <t>Puntos físicos del colegio/universidad (Cancha principal, Cafetería, Edificio A, etc.).</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: Selector de área en checkout.html
+    <t>🟡 Defecto abierto</t>
+  </si>
+  <si>
+    <t>Frontend: Selector de área en checkout.html
 Admin: CRUD de Áreas en admin.js
 BD: tabla areas_entrega</t>
   </si>
   <si>
+    <t>DEFECTO: crear un area devuelve HTTP 500 SIEMPRE. Causa: doble desestructuracion en ordenes.js:97 (queryLocal ya devuelve rows, no [rows]). Listar, editar y borrar si funcionan; las 4 areas semilla se sirven bien.</t>
+  </si>
+  <si>
     <t>REQ-17</t>
   </si>
   <si>
@@ -418,10 +510,13 @@
     <t>Permitir ordenar con pago en efectivo al recibir, registrando el cobro al momento de la entrega.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: checkout.html (Opción Efectivo)
+    <t>Frontend: checkout.html (Opción Efectivo)
 Backend: ordenAutomata.js y repartidor/entrega.html</t>
   </si>
   <si>
+    <t>Efectivo es el camino por defecto. La orden nace con estado_pago 'no_aplica' y pasa a 'pagado' al entregar.</t>
+  </si>
+  <si>
     <t>REQ-18</t>
   </si>
   <si>
@@ -431,7 +526,7 @@
     <t>Integración con pasarela Recurrente (https://www.recurrente.com/) con checkout seguro.</t>
   </si>
   <si>
-    <t>🟡 Pendiente Equipo</t>
+    <t>🟡 Falta configurar</t>
   </si>
   <si>
     <t>Actualmente implementado con Mock seguro de validación de tarjeta. Requiere conectar API Keys de Recurrente.</t>
@@ -440,6 +535,9 @@
     <t>Persona A</t>
   </si>
   <si>
+    <t>AVANCE NO REFLEJADO: el mock fue retirado. Hay cliente real (checkout alojado, la tarjeta nunca toca el servidor), webhook con control de reintentos y 3 columnas nuevas en BD. Solo faltan las claves del .env.</t>
+  </si>
+  <si>
     <t>REQ-19</t>
   </si>
   <si>
@@ -449,13 +547,19 @@
     <t>Verificación de bots antes de procesar el pago de la orden.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: checkout.html (Widget reCAPTCHA)
+    <t>🟡 Apagado por config</t>
+  </si>
+  <si>
+    <t>Frontend: checkout.html (Widget reCAPTCHA)
 Backend: backend/utils/recaptcha.js</t>
   </si>
   <si>
     <t>Persona D</t>
   </si>
   <si>
+    <t>OJO: el codigo esta completo pero HOY ESTA APAGADO. En .env: RECAPTCHA_SITE_KEY y SECRET vacias y RECAPTCHA_SKIP=true. En la practica el checkout no valida bots.</t>
+  </si>
+  <si>
     <t>REQ-20</t>
   </si>
   <si>
@@ -474,6 +578,9 @@
     <t>Persona B</t>
   </si>
   <si>
+    <t>WebSocket activo en /ws/tienda al arrancar (confirmado en el log). La suscripcion valida que la orden sea del usuario antes de emitir.</t>
+  </si>
+  <si>
     <t>REQ-21</t>
   </si>
   <si>
@@ -486,6 +593,9 @@
     <t>Backend: backend/utils/constanciaCompra.js (Descarga directa y guardado en servidor)</t>
   </si>
   <si>
+    <t>constanciaCompra.js genera el PDF con QR y el endpoint responde. Envio por correo no verificable sin SMTP real.</t>
+  </si>
+  <si>
     <t>REQ-22</t>
   </si>
   <si>
@@ -498,6 +608,9 @@
     <t>Frontend: /comprador/historial.html (Lista de órdenes + botón Reordenar)</t>
   </si>
   <si>
+    <t>GET /ordenes/mis y POST /ordenes/:id/reordenar presentes y respondiendo.</t>
+  </si>
+  <si>
     <t>REQ-23</t>
   </si>
   <si>
@@ -513,6 +626,9 @@
     <t>Frontend: /repartidor/entrega.html (HTML5-QRCode scanner integrado)</t>
   </si>
   <si>
+    <t>Html5Qrcode integrado y busqueda manual por codigo funcionando. El escaneo fisico requiere camara.</t>
+  </si>
+  <si>
     <t>REQ-24</t>
   </si>
   <si>
@@ -525,6 +641,9 @@
     <t>Frontend: /repartidor/entrega.html (Signature Pad Canvas + Foto de entrega)</t>
   </si>
   <si>
+    <t>Canvas de firma con eventos de raton Y tactiles (funciona en movil) + carga de foto de comprobante.</t>
+  </si>
+  <si>
     <t>REQ-25</t>
   </si>
   <si>
@@ -534,10 +653,13 @@
     <t>Opción para marcar entregas fallidas con registro de motivo para reprogramación.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend: Botón "No encontrado" en entrega.html
+    <t>Frontend: Botón "No encontrado" en entrega.html
 Backend: ordenAutomata.js (Transición a "no_encontrado")</t>
   </si>
   <si>
+    <t>La FSM define no_encontrado con retorno a en_ruta para reprogramar.</t>
+  </si>
+  <si>
     <t>REQ-26</t>
   </si>
   <si>
@@ -553,6 +675,9 @@
     <t>Frontend: /supervisor/dashboard.html y sección SPA en /admin/administrador.html (Chart.js)</t>
   </si>
   <si>
+    <t>Los tres rangos Hoy / Semana / Historico estan en AMBOS paneles (supervisor y admin).</t>
+  </si>
+  <si>
     <t>REQ-27</t>
   </si>
   <si>
@@ -565,6 +690,9 @@
     <t>Frontend: Gráfico Chart.js doughnut/bar y lista top productos en dashboard.js</t>
   </si>
   <si>
+    <t>Chart.js con grafico de estados y ranking de productos mas vendidos.</t>
+  </si>
+  <si>
     <t>REQ-28</t>
   </si>
   <si>
@@ -577,6 +705,9 @@
     <t>Frontend: Botón "Exportar CSV" en dashboard.js y ordenes.js</t>
   </si>
   <si>
+    <t>Exportacion CSV con BOM UTF-8 (abre bien en Excel con tildes) en dashboard y en ordenes.</t>
+  </si>
+  <si>
     <t>REQ-29</t>
   </si>
   <si>
@@ -589,11 +720,14 @@
     <t>Control de acceso por middleware y redirección automática según rol tras el login.</t>
   </si>
   <si>
-    <t xml:space="preserve">BD: tabla Roles (4, 5, 6, 7)
+    <t>BD: tabla Roles (4, 5, 6, 7)
 Backend: makeAuth middleware con control de roles
 Frontend: redirect.js</t>
   </si>
   <si>
+    <t>PROBADO A FONDO: /api/roles devuelve los 4 roles. Control de acceso verificado: sin token -&gt; 401, token de comprador -&gt; 403, token de admin -&gt; 200.</t>
+  </si>
+  <si>
     <t>REQ-30</t>
   </si>
   <si>
@@ -612,6 +746,9 @@
     <t>Persona F</t>
   </si>
   <si>
+    <t>Tres contenedores separados (nginx / node / mysql) levantados y sanos.</t>
+  </si>
+  <si>
     <t>REQ-31</t>
   </si>
   <si>
@@ -624,6 +761,9 @@
     <t>docker-compose.yml, backend/Dockerfile, frontend/Dockerfile, iniciar-proyecto.ps1/.sh</t>
   </si>
   <si>
+    <t>`docker compose up -d --build` levanto los 3 servicios a la primera. MySQL reporta healthy. Volumenes persistentes configurados.</t>
+  </si>
+  <si>
     <t>REQ-32</t>
   </si>
   <si>
@@ -636,6 +776,9 @@
     <t>Nginx security headers (CSP, nosniff, X-Frame-Options), mysql2 prepared params, rateLimit.js</t>
   </si>
   <si>
+    <t>Cabeceras comprobadas en la respuesta HTTP real: CSP completa, X-Frame-Options, nosniff, Referrer-Policy. Rate limit PROBADO: HTTP 429 tras 25 intentos. Cero concatenacion de SQL en todo el backend.</t>
+  </si>
+  <si>
     <t>REQ-33</t>
   </si>
   <si>
@@ -645,11 +788,14 @@
     <t>Registro de quién, qué acción, fecha/hora e IP de acceso en la base de datos.</t>
   </si>
   <si>
-    <t xml:space="preserve">BD: tabla auditoria
+    <t>BD: tabla auditoria
 Backend: backend/utils/auditLogger.js
 Admin: frontend/src/admin/js/auditoria.js</t>
   </si>
   <si>
+    <t>Funciona (19 filas en auditoria, 99 en access_logs) PERO no registra los intentos FALLIDOS: logAccess nunca se invoca con exitoso:false (login.js:203, 293, 375). La estadistica de accesos siempre dira 100% de exito y no se puede detectar fuerza bruta.</t>
+  </si>
+  <si>
     <t>REQ-34</t>
   </si>
   <si>
@@ -662,6 +808,9 @@
     <t>CSS: umg-glass.css, umg-auth-glass.css (Arquetipo Nómada Adrian Sáenz)</t>
   </si>
   <si>
+    <t>Tokens 60-30-10 definidos en umg-glass.css. Ningun asset roto: se comprobaron todas las referencias de las paginas publicas y todas devuelven 200.</t>
+  </si>
+  <si>
     <t>REQ-BONUS-1</t>
   </si>
   <si>
@@ -680,6 +829,9 @@
     <t>Backend: backend/utils/ordenAutomata.js</t>
   </si>
   <si>
+    <t>FSM probada en vivo: rechazo una transicion ilegal con HTTP 409 "La orden ya esta en estado final". El automata hace su trabajo.</t>
+  </si>
+  <si>
     <t>REQ-BONUS-2</t>
   </si>
   <si>
@@ -692,6 +844,9 @@
     <t>Backend: backend/utils/whatsappService.js y panel admin de vinculación QR</t>
   </si>
   <si>
+    <t>Baileys arranca y genera el QR de vinculacion al iniciar el servidor (confirmado en el log).</t>
+  </si>
+  <si>
     <t>DOC-01</t>
   </si>
   <si>
@@ -704,12 +859,21 @@
     <t>Presentación de funcionalidades, arquitectura y costos de implementación en idioma inglés.</t>
   </si>
   <si>
+    <t>🟡 Pendiente Equipo</t>
+  </si>
+  <si>
     <t>Crear archivo: docs/entrega/Presentacion_Ejecutiva_UMG_Personaliza.pptx</t>
   </si>
   <si>
     <t>Persona C</t>
   </si>
   <si>
+    <t>NO EXISTE. Es el unico entregable de la evaluacion final sin ningun avance junto con el video.</t>
+  </si>
+  <si>
+    <t>🟡 Archivo</t>
+  </si>
+  <si>
     <t>DOC-02</t>
   </si>
   <si>
@@ -725,6 +889,9 @@
     <t>Todo el Equipo</t>
   </si>
   <si>
+    <t>NO GRABADO. Requisito duro de la nota final y el de mayor riesgo porque depende de los 6 integrantes.</t>
+  </si>
+  <si>
     <t>DOC-03</t>
   </si>
   <si>
@@ -737,6 +904,9 @@
     <t>Generar archivos en: docs/entrega/uml/</t>
   </si>
   <si>
+    <t>YA ENTREGADO - la matriz estaba desactualizada. Estan casos-de-uso.drawio, diagrama-de-clases.drawio y arquitectura.drawio, mas sus PDF exportados.</t>
+  </si>
+  <si>
     <t>DOC-04</t>
   </si>
   <si>
@@ -749,6 +919,9 @@
     <t>Generar archivo: docs/entrega/flujo_compra_bizagi.bpm</t>
   </si>
   <si>
+    <t>YA ENTREGADO - la matriz estaba desactualizada. proceso-compra-entrega.bpmn validado como XML BPMN 2.0 correcto: 4 carriles (Comprador, Sistema, Taller, Repartidor), 16 tareas, 4 compuertas y 25 flujos. Importable en Bizagi.</t>
+  </si>
+  <si>
     <t>DOC-05</t>
   </si>
   <si>
@@ -761,6 +934,9 @@
     <t>Generar PDF: docs/entrega/Manual_Usuario_Comprador.pdf</t>
   </si>
   <si>
+    <t>NO EXISTE. Las guias que hay (compilacion y consumo de APIs) son tecnicas, no un manual para el comprador.</t>
+  </si>
+  <si>
     <t>DOC-06</t>
   </si>
   <si>
@@ -770,9 +946,15 @@
     <t>Colección JSON con endpoints de Auth, Tienda, Carrito, Órdenes, Admin y Repartidor documentados.</t>
   </si>
   <si>
+    <t>🟡 Entregado con fallos</t>
+  </si>
+  <si>
     <t>Exportar colección JSON en: docs/entrega/UMG_Personaliza.postman_collection.json</t>
   </si>
   <si>
+    <t>YA ENTREGADO pero CON DEFECTOS. Se ejecutaron las 59 peticiones contra el sistema: 37 OK y 10 ROTAS por campos mal puestos (ver pestana Pendientes).</t>
+  </si>
+  <si>
     <t>DOC-07</t>
   </si>
   <si>
@@ -785,6 +967,591 @@
     <t>Configurar servidor público y compartir URL en informe final.</t>
   </si>
   <si>
+    <t>Sigue solo en local: PUBLIC_URL=http://localhost:8082 y COOKIE_SECURE=false. Sin dominio ni certificado.</t>
+  </si>
+  <si>
+    <t>LO QUE FALTA — auditoría con el sistema en ejecución · 20/09/2026</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Qué falta</t>
+  </si>
+  <si>
+    <t>Detalle y evidencia concreta</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Esfuerzo</t>
+  </si>
+  <si>
+    <t>¿Por qué importa?</t>
+  </si>
+  <si>
+    <t>ENTREGABLES ACADEMICOS — sin ningun avance</t>
+  </si>
+  <si>
+    <t>P-01</t>
+  </si>
+  <si>
+    <t>Video explicativo (ingles, 5 min)</t>
+  </si>
+  <si>
+    <t>No existe. Deben aparecer los 6 integrantes explicando su modulo. Es el pendiente de mayor riesgo porque depende de coordinar a todo el equipo, no de programar.</t>
+  </si>
+  <si>
+    <t>Todo el equipo</t>
+  </si>
+  <si>
+    <t>🔴 Critica</t>
+  </si>
+  <si>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>Requisito duro de la Evaluacion Final. Sin esto no se cierra la nota.</t>
+  </si>
+  <si>
+    <t>P-02</t>
+  </si>
+  <si>
+    <t>Presentacion ejecutiva PPT (ingles)</t>
+  </si>
+  <si>
+    <t>No existe el archivo. Debe cubrir funcionalidades, arquitectura y costos de implementacion, en ingles.</t>
+  </si>
+  <si>
+    <t>Medio</t>
+  </si>
+  <si>
+    <t>Requisito de la Evaluacion Final. Ademas debe llevar el enlace del video.</t>
+  </si>
+  <si>
+    <t>P-03</t>
+  </si>
+  <si>
+    <t>Manual de Usuario del Comprador</t>
+  </si>
+  <si>
+    <t>No existe. Las dos guias que hay (compilacion y consumo de APIs) son tecnicas, no para el comprador. Falta el paso a paso ilustrado de registro, personalizacion, compra y tracking.</t>
+  </si>
+  <si>
+    <t>🔴 Alta</t>
+  </si>
+  <si>
+    <t>Requisito de la Evaluacion Final.</t>
+  </si>
+  <si>
+    <t>P-04</t>
+  </si>
+  <si>
+    <t>Despliegue publico con dominio y SSL</t>
+  </si>
+  <si>
+    <t>Sigue solo en local: PUBLIC_URL=http://localhost:8082 y COOKIE_SECURE=false. Falta VPS, dominio y certificado Lets Encrypt.</t>
+  </si>
+  <si>
+    <t>Requisito de la Evaluacion Final. Al publicar hay que poner COOKIE_SECURE=true.</t>
+  </si>
+  <si>
+    <t>DEFECTOS DE CODIGO ENCONTRADOS AL PROBAR EL SISTEMA</t>
+  </si>
+  <si>
+    <t>P-05</t>
+  </si>
+  <si>
+    <t>BUG: crear area de entrega rompe el servidor</t>
+  </si>
+  <si>
+    <t>POST /api/tienda/areas devuelve HTTP 500 SIEMPRE, con el mensaje (intermediate value) is not iterable. Causa exacta: ordenes.js linea 97 hace const [result] = await queryLocal(...) pero queryLocal ya devuelve rows (database.js:167). Se arregla quitando los corchetes.</t>
+  </si>
+  <si>
+    <t>15 min</t>
+  </si>
+  <si>
+    <t>REQ-16 esta marcado como cumplido y NO lo esta. El admin no puede dar de alta un area nueva durante la demo.</t>
+  </si>
+  <si>
+    <t>P-06</t>
+  </si>
+  <si>
+    <t>BUG: la bitacora no registra intentos fallidos</t>
+  </si>
+  <si>
+    <t>access_logs tiene 99 filas y las 99 son exitosas. logAccess() nunca se llama con exitoso:false (login.js lineas 203, 293 y 375). El parametro existe pero ninguna llamada lo usa.</t>
+  </si>
+  <si>
+    <t>🟠 Media</t>
+  </si>
+  <si>
+    <t>30 min</t>
+  </si>
+  <si>
+    <t>REQ-33 pide una bitacora auditable. Hoy no se puede detectar fuerza bruta ni mostrar accesos denegados; la estadistica siempre dira 100% de exito.</t>
+  </si>
+  <si>
+    <t>P-07</t>
+  </si>
+  <si>
+    <t>BUG: el canal de notificacion se guarda mal por API</t>
+  </si>
+  <si>
+    <t>Enviar notif_whatsapp=0 lo guarda como activado, porque en JavaScript la cadena 0 es verdadera (registro.js lineas 74-75). Por la web funciona bien (la casilla sin marcar no se envia), pero por API no.</t>
+  </si>
+  <si>
+    <t>20 min</t>
+  </si>
+  <si>
+    <t>REQ-02 dice que el comprador elige su canal. Con el collection de Postman se le activa WhatsApp aunque lo haya rechazado.</t>
+  </si>
+  <si>
+    <t>P-08</t>
+  </si>
+  <si>
+    <t>Postman: 10 de las 59 peticiones fallan</t>
+  </si>
+  <si>
+    <t>Ejecutadas todas contra el sistema. Fallan: Registro (faltan nombres, apellidos y nombre_usuario), Validar unico (manda campo/valor en vez de correo/usuario), Login QR, Reenviar codigo, Recuperar y Restablecer contrasena, Cambiar rol, Activar usuario (manda estado y el backend espera nuevoEstado), Listar repartidores (apunta a /admin/conductores, que no existe) y Editar producto (PUT parcial).</t>
+  </si>
+  <si>
+    <t>2 h</t>
+  </si>
+  <si>
+    <t>DOC-06 es un entregable calificado. Si el catedratico lo ejecuta tal cual, 10 peticiones le dan error.</t>
+  </si>
+  <si>
+    <t>P-09</t>
+  </si>
+  <si>
+    <t>Validar las entradas antes de tocar la base</t>
+  </si>
+  <si>
+    <t>PUT /productos/:id y PUT /usuarios/:id/estado devuelven HTTP 500 cuando falta un campo, en vez de 400. El error real en el log era: Bind parameters must not contain undefined.</t>
+  </si>
+  <si>
+    <t>🟢 Baja</t>
+  </si>
+  <si>
+    <t>45 min</t>
+  </si>
+  <si>
+    <t>Un 500 significa que el servidor se rompio. Ante datos incompletos debe responder 400, no reventar.</t>
+  </si>
+  <si>
+    <t>CONFIGURACION — el codigo ya esta, faltan las llaves</t>
+  </si>
+  <si>
+    <t>P-10</t>
+  </si>
+  <si>
+    <t>Claves de la pasarela Recurrente</t>
+  </si>
+  <si>
+    <t>El codigo ya es real y completo (el mock fue retirado): cliente de checkout alojado, webhook y 3 columnas en BD. Solo faltan RECURRENTE_PUBLIC_KEY y RECURRENTE_SECRET_KEY en el .env. Conviene empezar por el entorno Sandbox, que no mueve dinero real.</t>
+  </si>
+  <si>
+    <t>1 h</t>
+  </si>
+  <si>
+    <t>Es lo unico que separa a REQ-18 de estar cerrado. Sin claves, el pago con tarjeta responde 503.</t>
+  </si>
+  <si>
+    <t>P-11</t>
+  </si>
+  <si>
+    <t>Verificar la firma del webhook</t>
+  </si>
+  <si>
+    <t>Queda un TODO explicito en ordenes.js linea 351. Hoy el webhook se protege con un secreto dentro de la URL, que sirve, pero falta validar la firma que manda Recurrente en la cabecera.</t>
+  </si>
+  <si>
+    <t>Sin firma, quien adivine la URL podria marcar una orden como pagada sin haber pagado.</t>
+  </si>
+  <si>
+    <t>P-12</t>
+  </si>
+  <si>
+    <t>Claves de reCAPTCHA y quitar el SKIP</t>
+  </si>
+  <si>
+    <t>En el .env: RECAPTCHA_SITE_KEY y RECAPTCHA_SECRET_KEY estan vacias y RECAPTCHA_SKIP=true. El codigo esta completo en frontend y backend; solo falta configurarlo.</t>
+  </si>
+  <si>
+    <t>REQ-19 figura como cumplido pero hoy esta apagado: el checkout no valida bots y no se puede demostrar en la defensa.</t>
+  </si>
+  <si>
+    <t>DATOS Y CONTENIDO</t>
+  </si>
+  <si>
+    <t>P-13</t>
+  </si>
+  <si>
+    <t>Fotografias reales de los productos</t>
+  </si>
+  <si>
+    <t>Los 6 productos tienen imagen_url = NULL. En todo el proyecto solo hay 4 imagenes: los 3 filtros faciales y el logo de la UMG.</t>
+  </si>
+  <si>
+    <t>El catalogo se ve vacio en la demo, y es lo primero que ve el catedratico al abrir la tienda.</t>
+  </si>
+  <si>
+    <t>P-14</t>
+  </si>
+  <si>
+    <t>Completar el catalogo a 12 productos</t>
+  </si>
+  <si>
+    <t>La matriz decia 12 productos base pero la base sirve 6 (02-ecommerce.sql). O se suben 6 mas, o se corrige el documento.</t>
+  </si>
+  <si>
+    <t>Coherencia entre lo que se entrega por escrito y lo que ensena el sistema.</t>
+  </si>
+  <si>
+    <t>PRIMERA REVISIÓN (2 pts) — PRUEBAS CON EL SISTEMA EN EJECUCIÓN · 20/09/2026</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Requisito de la 1ra Revisión</t>
+  </si>
+  <si>
+    <t>Prueba ejecutada</t>
+  </si>
+  <si>
+    <t>Resultado obtenido</t>
+  </si>
+  <si>
+    <t>Veredicto</t>
+  </si>
+  <si>
+    <t>Observación</t>
+  </si>
+  <si>
+    <t>REQUISITO 1 — DIAGRAMA DE FLUJO EN BIZAGI</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Diagrama BIZAGI</t>
+  </si>
+  <si>
+    <t>Validar proceso-compra-entrega.bpmn como XML BPMN 2.0 y contar sus elementos.</t>
+  </si>
+  <si>
+    <t>XML valido. 4 carriles (Comprador, Sistema, Taller, Repartidor), 16 tareas, 4 compuertas, 2 fines, 25 flujos.</t>
+  </si>
+  <si>
+    <t>✅ Pasa</t>
+  </si>
+  <si>
+    <t>BPMN 2.0 estandar, importable en Bizagi. Ademas exportado a PDF.</t>
+  </si>
+  <si>
+    <t>REQUISITO 2 — DIAGRAMA DE BASE DE DATOS</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Diagrama ER</t>
+  </si>
+  <si>
+    <t>Listar las tablas reales de MySQL y contrastarlas con DIAGRAMA_ER.md.</t>
+  </si>
+  <si>
+    <t>15 tablas en la base y las 15 documentadas. Ninguna sin documentar.</t>
+  </si>
+  <si>
+    <t>Incluye ademas arquitectura.drawio y los PDF exportados.</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>La base arranca limpia</t>
+  </si>
+  <si>
+    <t>docker compose up -d --build partiendo de cero.</t>
+  </si>
+  <si>
+    <t>MySQL 8.0 healthy. Los scripts 02, 05 y 06 corrieron sin abortar.</t>
+  </si>
+  <si>
+    <t>El fallo del USE en 06-pagos-recurrente.sql ya estaba corregido.</t>
+  </si>
+  <si>
+    <t>REQUISITO 3 — REGISTRO DE USUARIO Y LOGIN</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Validacion de unicidad</t>
+  </si>
+  <si>
+    <t>POST /validar_unico con un correo existente y con uno nuevo.</t>
+  </si>
+  <si>
+    <t>Repetido: 'El correo ya esta registrado'. Nuevo: '1' (libre).</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Campos obligatorios</t>
+  </si>
+  <si>
+    <t>POST /registro enviando solo el nombre.</t>
+  </si>
+  <si>
+    <t>HTTP 400 'Faltan campos obligatorios'.</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Registro completo</t>
+  </si>
+  <si>
+    <t>POST /registro con todos los datos de un comprador nuevo.</t>
+  </si>
+  <si>
+    <t>HTTP 201. Usuario id 783 creado y confirmado en la tabla usuarios.</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>Contrasena cifrada</t>
+  </si>
+  <si>
+    <t>Consultar el hash directamente en MySQL.</t>
+  </si>
+  <si>
+    <t>Hash $2b$10$... de 60 caracteres: bcrypt con 10 salt rounds.</t>
+  </si>
+  <si>
+    <t>Cumple el REQ-03 tal como lo pide el documento.</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Rol automatico de Comprador</t>
+  </si>
+  <si>
+    <t>Revisar Id_Rol_Usuario del usuario recien creado.</t>
+  </si>
+  <si>
+    <t>rol = 6 (Comprador), asignado sin intervencion.</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>OTP con codigo incorrecto</t>
+  </si>
+  <si>
+    <t>POST /verify-registration-code con el codigo 000000.</t>
+  </si>
+  <si>
+    <t>HTTP 400 'Codigo invalido o expirado'.</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>OTP con codigo correcto</t>
+  </si>
+  <si>
+    <t>Leer el codigo real de la tabla verificaciones y enviarlo.</t>
+  </si>
+  <si>
+    <t>HTTP 200 'Usuario verificado correctamente'.</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>No se entra sin verificar</t>
+  </si>
+  <si>
+    <t>Registrar un usuario nuevo e intentar login SIN verificar el OTP.</t>
+  </si>
+  <si>
+    <t>HTTP 401. En la base queda activo=0 y correo_ver=0 hasta verificar.</t>
+  </si>
+  <si>
+    <t>La puerta de verificacion funciona correctamente.</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>Login de los 4 roles</t>
+  </si>
+  <si>
+    <t>POST /login con admin, supervisor, repartidor y test.</t>
+  </si>
+  <si>
+    <t>Los 4 devuelven HTTP 200 con token JWT valido.</t>
+  </si>
+  <si>
+    <t>Las credenciales de la pestana Roles funcionan tal como estan escritas.</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <t>Contenido del JWT</t>
+  </si>
+  <si>
+    <t>Decodificar el token del administrador.</t>
+  </si>
+  <si>
+    <t>Trae sub, uid, usuario, correo, rol 'Administrador', mfa, iss, aud y exp de 15 min.</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <t>Contrasena incorrecta</t>
+  </si>
+  <si>
+    <t>POST /login con la contrasena equivocada.</t>
+  </si>
+  <si>
+    <t>HTTP 401 'Usuario o contrasena invalidos'.</t>
+  </si>
+  <si>
+    <t>Mismo mensaje para usuario inexistente: no revela si la cuenta existe.</t>
+  </si>
+  <si>
+    <t>3.12</t>
+  </si>
+  <si>
+    <t>Control de acceso por rol</t>
+  </si>
+  <si>
+    <t>GET /admin/usuarios sin token, con token de comprador y con token de admin.</t>
+  </si>
+  <si>
+    <t>Sin token 401 · Comprador 403 · Admin 200.</t>
+  </si>
+  <si>
+    <t>El middleware de roles hace exactamente lo que debe.</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t>Proteccion de fuerza bruta</t>
+  </si>
+  <si>
+    <t>Repetir intentos de login hasta pasar el limite.</t>
+  </si>
+  <si>
+    <t>HTTP 429 'Demasiados intentos de acceso. Espera 95 segundos'.</t>
+  </si>
+  <si>
+    <t>Rate limit activo: 25 intentos por cada 5 minutos.</t>
+  </si>
+  <si>
+    <t>3.14</t>
+  </si>
+  <si>
+    <t>Bitacora de accesos</t>
+  </si>
+  <si>
+    <t>Consultar las tablas auditoria y access_logs.</t>
+  </si>
+  <si>
+    <t>19 filas en auditoria y 99 en access_logs, pero las 99 son exitosas.</t>
+  </si>
+  <si>
+    <t>Los intentos fallidos no se registran nunca. Ver P-06 en Pendientes.</t>
+  </si>
+  <si>
+    <t>REQUISITO 4 — SITIO PUBLICO</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Paginas publicas</t>
+  </si>
+  <si>
+    <t>Pedir por HTTP las 10 rutas principales del sitio.</t>
+  </si>
+  <si>
+    <t>Las 10 devuelven HTTP 200: inicio, recuperar, tienda, tracking, dashboard, entrega, admin, CSS y JS.</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>API publica sin sesion</t>
+  </si>
+  <si>
+    <t>GET a config, roles, productos, categorias y areas.</t>
+  </si>
+  <si>
+    <t>Las 5 devuelven 200. Roles trae los 4 correctos; areas trae las 4 del campus.</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Ningun recurso roto</t>
+  </si>
+  <si>
+    <t>Extraer todos los src y href de las paginas y pedirlos uno a uno.</t>
+  </si>
+  <si>
+    <t>Ni un solo 404. Todos los CSS, JS e imagenes cargan.</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>Cabeceras de seguridad</t>
+  </si>
+  <si>
+    <t>Inspeccionar las cabeceras de la respuesta HTTP real.</t>
+  </si>
+  <si>
+    <t>CSP completa, X-Frame-Options, X-Content-Type-Options nosniff y Referrer-Policy presentes.</t>
+  </si>
+  <si>
+    <t>Cubre el REQ-32 de desarrollo seguro OWASP.</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>Catalogo con datos</t>
+  </si>
+  <si>
+    <t>GET /api/tienda/productos.</t>
+  </si>
+  <si>
+    <t>6 productos con precio, stock y lado B. Los 6 con imagen_url = NULL.</t>
+  </si>
+  <si>
+    <t>Funciona, pero sin fotos el catalogo se ve vacio. Ver P-13.</t>
+  </si>
+  <si>
+    <t>VEREDICTO: 20 pruebas pasan, 2 parciales, 0 fallan. Los cuatro requisitos de la 1ra Revisión (Bizagi, diagrama de BD, registro + login y sitio público) están cumplidos y son demostrables en vivo.</t>
+  </si>
+  <si>
     <t>PLAN DE ASIGNACIÓN DE TAREAS POR INTEGRANTE (EQUIPO DE DESARROLLO)</t>
   </si>
   <si>
@@ -800,9 +1567,6 @@
     <t>Tareas Específicas a Realizar</t>
   </si>
   <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
     <t>Entregables Concretos</t>
   </si>
   <si>
@@ -812,16 +1576,13 @@
     <t>Integraciones &amp; Pasarela de Pagos</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Integrar API de Recurrente (Sandbox/Producción) en checkout.
+    <t>1. Integrar API de Recurrente (Sandbox/Producción) en checkout.
 2. Conectar Webhook de confirmación de pago.
 3. Guardar ref_pago en BD.
 4. Crear colección Postman con endpoints de Checkout y Auth.</t>
   </si>
   <si>
-    <t>🔴 Alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Código integración Recurrente
+    <t>• Código integración Recurrente
 • Postman Collection JSON exportado
 • 3 casos de prueba (aprobado/rechazado)</t>
   </si>
@@ -835,15 +1596,12 @@
     <t>UX, Tracking &amp; Notificaciones</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Verificar flujo de tracking en vivo WebSocket (/ws/tienda).
+    <t>1. Verificar flujo de tracking en vivo WebSocket (/ws/tienda).
 2. Probar envío de constancias PDF por correo/WhatsApp.
 3. Añadir micro-animaciones o alertas visuales al cambiar de estado.</t>
   </si>
   <si>
-    <t>🟠 Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Pruebas de tracking validadas
+    <t>• Pruebas de tracking validadas
 • Verificación de plantilla de correos y WhatsApp</t>
   </si>
   <si>
@@ -856,13 +1614,13 @@
     <t>Documentación Académica &amp; UML</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Elaborar Diagrama de Flujo en BIZAGI (Proceso de compra y entrega).
+    <t>1. Elaborar Diagrama de Flujo en BIZAGI (Proceso de compra y entrega).
 2. Crear Diagramas UML en StarUML (Casos de uso, clases, arquitectura).
 3. Redactar Manual de Usuario del Comprador con capturas.
 4. Coordinar presentación PPT en inglés.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Archivo Bizagi (.bpm/.pdf)
+    <t>• Archivo Bizagi (.bpm/.pdf)
 • Diagramas UML exportados
 • Manual de Usuario en PDF
 • PPT de exposición en inglés</t>
@@ -877,13 +1635,13 @@
     <t>Seguridad, Auditoría &amp; QA</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Validar registros en tabla auditoria (quién, qué, cuándo, IP).
+    <t>1. Validar registros en tabla auditoria (quién, qué, cuándo, IP).
 2. Verificar sanitización y protección OWASP en endpoints.
 3. Ejecutar script de pruebas automáticas qa-tienda-smoke.ps1 (35/35).
 4. Configurar reCAPTCHA en producción.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Reporte de Auditoría y QA validado
+    <t>• Reporte de Auditoría y QA validado
 • Checklist de seguridad OWASP</t>
   </si>
   <si>
@@ -893,13 +1651,13 @@
     <t>Datos de Prueba &amp; Catálogo</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Cargar fotografías reales de artículos del campus en catálogo.
+    <t>1. Cargar fotografías reales de artículos del campus en catálogo.
 2. Configurar stock inicial y nombres de Áreas de Entrega del campus.
 3. Crear usuarios de prueba adicionales con rol Repartidor y Comprador.
 4. Validar exportación de CSV en Dashboard de Ventas.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Script SQL con catálogo final poblado
+    <t>• Script SQL con catálogo final poblado
 • Fotos de productos optimizadas
 • Reporte de stock verificado</t>
   </si>
@@ -913,13 +1671,13 @@
     <t>DevOps &amp; Despliegue en Servidor</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Desplegar aplicación en servidor público (Docker Compose en VPS).
+    <t>1. Desplegar aplicación en servidor público (Docker Compose en VPS).
 2. Configurar dominio público con certificado SSL (Let's Encrypt / HTTPS).
 3. Validar volumen persistente para base de datos y uploads.
 4. Asegurar repositorio Git con cuenta del catedrático añadida.</t>
   </si>
   <si>
-    <t xml:space="preserve">• URL pública accesible con HTTPS
+    <t>• URL pública accesible con HTTPS
 • Guía de compilación y despliegue (Backend/Frontend)
 • Repo Git actualizado y compartido</t>
   </si>
@@ -930,7 +1688,7 @@
     <t>Video Demostrativo del Proyecto</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Grabar video explicativo técnico y funcional (5 min máximo en idioma INGLÉS).
+    <t>1. Grabar video explicativo técnico y funcional (5 min máximo en idioma INGLÉS).
 2. Cada integrante debe aparecer explicando su módulo respectivo.
 3. Subir video y agregar enlace en la presentación ejecutiva.</t>
   </si>
@@ -1016,7 +1774,7 @@
     <t>COMPRADOR</t>
   </si>
   <si>
-    <t xml:space="preserve">test / test123
+    <t>test / test123
 (O nuevo registro)</t>
   </si>
   <si>
@@ -1029,164 +1787,164 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="32" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
+      <color rgb="FF2B2520"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF64748B"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF475569"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF166534"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF92400E"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF1E40AF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF8A3E22"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2B2520"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF166534"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF92400E"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF2B2520"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF2B2520"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF8A3E22"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF166534"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF92400E"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF8A3E22"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF2B2520"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF475569"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <color rgb="FF2B2520"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF1E40AF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF2B2520"/>
-      <sz val="11"/>
+      <sz val="9.5"/>
+      <color rgb="FF64748B"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF64748B"/>
       <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF475569"/>
-      <sz val="18"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF166534"/>
-      <sz val="18"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF92400E"/>
-      <sz val="18"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E40AF"/>
-      <sz val="18"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF8A3E22"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <color rgb="FF2B2520"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF166534"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF92400E"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF2B2520"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF2B2520"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF8A3E22"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF166534"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF92400E"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF8A3E22"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF2B2520"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF475569"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF2B2520"/>
-      <sz val="8.5"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E40AF"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF64748B"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF2B2520"/>
-      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1195,8 +1953,8 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="9"/>
       <color rgb="FF334155"/>
-      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1206,14 +1964,19 @@
     </font>
     <font>
       <b/>
+      <sz val="9.5"/>
       <color rgb="FF2B2520"/>
-      <sz val="9.5"/>
       <name val="Consolas"/>
     </font>
     <font>
+      <sz val="9"/>
       <color rgb="FF1D4ED8"/>
-      <sz val="9"/>
       <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2B2520"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1264,7 +2027,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1287,37 +2050,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE0D6CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0D6CE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE0D6CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0D6CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0D6CE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE0D6CE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE0D6CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0D6CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0D6CE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1357,71 +2135,146 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1761,9 +2614,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H26"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -1773,377 +2626,389 @@
     <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="3" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+    </row>
+    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="47"/>
+      <c r="D5" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="47"/>
+      <c r="F5" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="47"/>
+      <c r="H5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="35" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="7">
+    <row r="6" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="48">
+        <v>43</v>
+      </c>
+      <c r="C6" s="47"/>
+      <c r="D6" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="47"/>
+      <c r="F6" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="47"/>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6">
+        <v>8</v>
+      </c>
+      <c r="D10" s="6">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="9">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9">
+        <v>3</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="9">
+        <v>5</v>
+      </c>
+      <c r="D13" s="9">
+        <v>3</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="9">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9">
+        <v>3</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="6">
+        <v>4</v>
+      </c>
+      <c r="D16" s="6">
+        <v>4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="9">
+        <v>5</v>
+      </c>
+      <c r="D17" s="9">
+        <v>4</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="6">
+        <v>7</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3</v>
+      </c>
+      <c r="E18" s="6">
+        <v>4</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="51"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="51"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="14">
-        <v>7</v>
-      </c>
-      <c r="D10" s="14">
-        <v>7</v>
-      </c>
-      <c r="E10" s="14">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="17">
-        <v>4</v>
-      </c>
-      <c r="D11" s="17">
-        <v>4</v>
-      </c>
-      <c r="E11" s="17">
-        <v>0</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="14">
-        <v>6</v>
-      </c>
-      <c r="D12" s="14">
-        <v>6</v>
-      </c>
-      <c r="E12" s="14">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="17">
-        <v>6</v>
-      </c>
-      <c r="D13" s="17">
-        <v>5</v>
-      </c>
-      <c r="E13" s="17">
-        <v>1</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="14">
-        <v>4</v>
-      </c>
-      <c r="D14" s="14">
-        <v>4</v>
-      </c>
-      <c r="E14" s="14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="17">
-        <v>4</v>
-      </c>
-      <c r="D15" s="17">
-        <v>4</v>
-      </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="17">
-        <v>7</v>
-      </c>
-      <c r="D17" s="17">
-        <v>7</v>
-      </c>
-      <c r="E17" s="17">
-        <v>0</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="14">
-        <v>6</v>
-      </c>
-      <c r="D18" s="14">
-        <v>0</v>
-      </c>
-      <c r="E18" s="14">
-        <v>6</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
+      <c r="C24" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="51"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="25" t="s">
+      <c r="G24" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="22" t="s">
+    <row r="25" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C25" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="24" t="s">
+      <c r="D25" s="51"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="26" t="s">
+    </row>
+    <row r="26" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="14" t="s">
         <v>48</v>
       </c>
+      <c r="C26" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="C24:E24"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="C26:E26"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -2152,1044 +3017,2263 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="28" t="s">
+    <row r="1" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+    </row>
+    <row r="2" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="B2" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="C2" s="18" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="D2" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="E2" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="F2" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="G2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="H2" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="I2" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="29" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="B3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="31" t="s">
+      <c r="C3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D3" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="34" t="s">
+      <c r="E3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="F3" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="31" t="s">
+      <c r="G3" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="H3" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="34" t="s">
+      <c r="I3" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="31" t="s">
+      <c r="B4" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D4" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="34" t="s">
+      <c r="E4" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="F4" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="31" t="s">
+      <c r="G4" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="I4" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="34" t="s">
+      <c r="B5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="D5" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="31" t="s">
+      <c r="E5" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="G5" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="34" t="s">
+      <c r="I5" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="B6" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="31" t="s">
+      <c r="D6" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="E6" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="34" t="s">
+      <c r="G6" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="I6" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="31" t="s">
+    </row>
+    <row r="7" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="B7" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="34" t="s">
+      <c r="D7" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="E7" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="G7" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="I7" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="32" t="s">
+    </row>
+    <row r="8" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="34" t="s">
+      <c r="B8" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="D8" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="31" t="s">
+      <c r="E8" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="G8" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="34" t="s">
+      <c r="I8" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="B9" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="31" t="s">
+      <c r="D9" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="E9" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="34" t="s">
+      <c r="G9" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="I9" s="42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B10" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="D10" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="E10" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="34" t="s">
+      <c r="G10" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="I10" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="31" t="s">
+      <c r="B11" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="C11" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="34" t="s">
+      <c r="D11" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="E11" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="31" t="s">
+      <c r="G11" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="I11" s="42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="34" t="s">
+      <c r="B12" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="D12" s="22" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="E12" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="G12" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="I12" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="B13" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="34" t="s">
+      <c r="D13" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="E13" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="31" t="s">
+      <c r="G13" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="I13" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="34" t="s">
+      <c r="B14" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="C14" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="31" t="s">
+      <c r="D14" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="E14" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="34" t="s">
+      <c r="G14" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="I14" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="31" t="s">
+      <c r="B15" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D15" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E15" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="G15" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="I15" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="B16" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="31" t="s">
+      <c r="D16" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="E16" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="E21" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="34" t="s">
+      <c r="G16" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="H16" s="41" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="I16" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B17" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C17" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D17" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="E22" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="34" t="s">
+      <c r="E17" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G17" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="41" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="I17" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B18" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C18" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D18" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="34" t="s">
+      <c r="E18" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="F18" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="G18" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C24" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="34" t="s">
+      <c r="C19" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="G24" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="D19" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="E19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="G19" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="I19" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="E25" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="34" t="s">
+      <c r="B20" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
+      <c r="D20" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="C26" s="31" t="s">
+      <c r="E20" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="F20" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="E26" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="34" t="s">
+      <c r="G20" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="G26" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="H20" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="B27" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="C27" s="31" t="s">
+      <c r="I20" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="B21" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="E27" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="34" t="s">
+      <c r="D21" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="G27" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+      <c r="E21" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="F21" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="G21" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="H21" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="34" t="s">
+      <c r="I21" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="B22" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="B29" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C29" s="31" t="s">
+      <c r="C22" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D22" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F29" s="34" t="s">
+      <c r="E22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="G29" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
+      <c r="G22" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="B30" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C30" s="31" t="s">
+      <c r="H22" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="I22" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="E30" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="34" t="s">
+      <c r="B23" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="29" t="s">
+      <c r="D23" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="E23" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="G23" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="I23" s="42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E31" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="34" t="s">
+      <c r="B24" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G31" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
+      <c r="D24" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="E24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="G24" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="I24" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="E32" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="B25" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="C25" s="21" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="33" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
+      <c r="D25" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B33" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33" s="31" t="s">
+      <c r="E25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="G25" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="34" t="s">
+      <c r="I25" s="42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="G33" s="29" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
+      <c r="B26" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B34" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="C34" s="31" t="s">
+      <c r="D26" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="E26" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" s="34" t="s">
+      <c r="G26" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="G34" s="29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="I26" s="43" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="B35" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="C35" s="31" t="s">
+      <c r="B27" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D27" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="E35" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F35" s="34" t="s">
+      <c r="E27" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="G35" s="29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="s">
+      <c r="G27" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="B36" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="C36" s="31" t="s">
+      <c r="I27" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="B28" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="E36" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="34" t="s">
+      <c r="C28" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="G36" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="29" t="s">
+      <c r="D28" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="30" t="s">
+      <c r="E28" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="G28" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="I28" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E37" s="36" t="s">
+      <c r="B29" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="F37" s="34" t="s">
+      <c r="D29" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="G37" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
+      <c r="E29" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="B38" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" s="31" t="s">
+      <c r="G29" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="I29" s="43" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="E38" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="F38" s="34" t="s">
+      <c r="B30" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="G38" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="29" t="s">
+      <c r="D30" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="B39" s="30" t="s">
+      <c r="E30" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="G30" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H30" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="I30" s="43" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="E39" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F39" s="34" t="s">
+      <c r="B31" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="G39" s="29" t="s">
+      <c r="C31" s="21" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="40" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="29" t="s">
+      <c r="D31" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B40" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="31" t="s">
+      <c r="E31" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="G31" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="E40" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F40" s="34" t="s">
+      <c r="I31" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="G40" s="29" t="s">
+      <c r="B32" s="20" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="41" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="29" t="s">
+      <c r="C32" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="B41" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C41" s="31" t="s">
+      <c r="D32" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="E32" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="E41" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F41" s="34" t="s">
+      <c r="G32" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="G41" s="29" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="H32" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="B42" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C42" s="31" t="s">
+      <c r="I32" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="B33" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="E42" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F42" s="34" t="s">
+      <c r="D33" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="G42" s="29" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="29" t="s">
+      <c r="E33" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="B43" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C43" s="31" t="s">
+      <c r="G33" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="H33" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="I33" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="E43" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F43" s="34" t="s">
+      <c r="B34" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="G43" s="29" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="29" t="s">
+      <c r="D34" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="B44" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C44" s="31" t="s">
+      <c r="E34" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="G34" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="H34" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="E44" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F44" s="34" t="s">
+      <c r="I34" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="G44" s="29" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="29" t="s">
+      <c r="B35" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="B45" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C45" s="31" t="s">
+      <c r="D35" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="E35" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="E45" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F45" s="34" t="s">
+      <c r="G35" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="H35" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="G45" s="29" t="s">
-        <v>193</v>
+      <c r="I35" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="I36" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H38" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="I38" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="I39" s="42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="H40" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="I40" s="42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E41" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H41" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="I41" s="42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H42" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="I42" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="E43" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H43" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="I43" s="42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="E44" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H44" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="I44" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="E45" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="H45" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="I45" s="40" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+    </row>
+    <row r="2" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="61" t="s">
+        <v>317</v>
+      </c>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+    </row>
+    <row r="4" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
+    </row>
+    <row r="9" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>340</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>343</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>354</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>358</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="F12" s="44" t="s">
+        <v>359</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>363</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="52"/>
+    </row>
+    <row r="15" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>368</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>370</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>379</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="61" t="s">
+        <v>381</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="52"/>
+    </row>
+    <row r="19" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>382</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>383</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>384</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>359</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>387</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>389</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+    </row>
+    <row r="2" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>391</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+    </row>
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>400</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="52"/>
+    </row>
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>405</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>411</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>412</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>413</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="61" t="s">
+        <v>415</v>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="52"/>
+    </row>
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F9" s="41"/>
+    </row>
+    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>421</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>422</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F10" s="41"/>
+    </row>
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>424</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>427</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F11" s="41"/>
+    </row>
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>428</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>430</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>431</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F13" s="41"/>
+    </row>
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>437</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>439</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>440</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F14" s="41"/>
+    </row>
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>441</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>444</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F15" s="41"/>
+    </row>
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>445</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>447</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>448</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>450</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>453</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
+        <v>455</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>456</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>457</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F18" s="41"/>
+    </row>
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>460</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>462</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>464</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>465</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>469</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>471</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>472</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>475</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>476</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="61" t="s">
+        <v>479</v>
+      </c>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52"/>
+    </row>
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>480</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>482</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>483</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F24" s="41"/>
+    </row>
+    <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>484</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>485</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>486</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>487</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F25" s="41"/>
+    </row>
+    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>489</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>490</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>491</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F26" s="41"/>
+    </row>
+    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
+        <v>492</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>493</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>494</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>495</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
+        <v>497</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>498</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>499</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>500</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="41" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="63" t="s">
+        <v>502</v>
+      </c>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -3200,199 +5284,199 @@
     <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>260</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>261</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>266</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>261</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="G5" s="35" t="s">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+    </row>
+    <row r="2" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>505</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>506</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>507</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>508</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>512</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>515</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="D7" s="39" t="s">
+      <c r="B5" s="28" t="s">
+        <v>519</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>528</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>530</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>533</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>534</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>535</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>536</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>261</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>292</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>263</v>
+      <c r="B9" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>539</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>541</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -3400,14 +5484,14 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3417,114 +5501,114 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-    </row>
-    <row r="2" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>300</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>302</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>304</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>306</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>313</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>318</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>319</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>305</v>
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
+        <v>542</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+    </row>
+    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>543</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>545</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>546</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>549</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>552</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>553</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>555</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>557</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>558</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>559</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>562</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>563</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>565</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>568</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -3532,6 +5616,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>